--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>127633119</v>
       </c>
       <c r="B36" t="n">
-        <v>103927</v>
+        <v>104317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>127633119</v>
       </c>
       <c r="B36" t="n">
-        <v>104317</v>
+        <v>104404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>127633119</v>
       </c>
       <c r="B36" t="n">
-        <v>104404</v>
+        <v>104407</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>127633119</v>
       </c>
       <c r="B36" t="n">
-        <v>104407</v>
+        <v>104433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>127633119</v>
       </c>
       <c r="B36" t="n">
-        <v>104433</v>
+        <v>104434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>127633119</v>
       </c>
       <c r="B36" t="n">
-        <v>104434</v>
+        <v>104435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>127633119</v>
       </c>
       <c r="B36" t="n">
-        <v>104435</v>
+        <v>104437</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5034,7 +5034,7 @@
         <v>127633119</v>
       </c>
       <c r="B36" t="n">
-        <v>104437</v>
+        <v>104441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3045,12 +3045,7 @@
         <v>69559093</v>
       </c>
       <c r="B20" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98932</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>709283.0899422318</v>
+        <v>709283</v>
       </c>
       <c r="R20" t="n">
-        <v>6663499.373136242</v>
+        <v>6663499</v>
       </c>
       <c r="S20" t="n">
         <v>100</v>
@@ -3115,19 +3110,9 @@
           <t>2004-01-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3166,12 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3203,10 +3183,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>709283.0899422318</v>
+        <v>709283</v>
       </c>
       <c r="R21" t="n">
-        <v>6663499.373136242</v>
+        <v>6663499</v>
       </c>
       <c r="S21" t="n">
         <v>100</v>
@@ -3236,19 +3216,9 @@
           <t>2004-01-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3287,12 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3324,10 +3289,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>709283.0899422318</v>
+        <v>709283</v>
       </c>
       <c r="R22" t="n">
-        <v>6663499.373136242</v>
+        <v>6663499</v>
       </c>
       <c r="S22" t="n">
         <v>100</v>
@@ -3357,19 +3322,9 @@
           <t>2004-01-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3408,12 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>99121</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3445,10 +3395,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>709283.0899422318</v>
+        <v>709283</v>
       </c>
       <c r="R23" t="n">
-        <v>6663499.373136242</v>
+        <v>6663499</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -3478,19 +3428,9 @@
           <t>2004-01-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3045,7 +3045,7 @@
         <v>69559093</v>
       </c>
       <c r="B20" t="n">
-        <v>98932</v>
+        <v>98933</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>99071</v>
+        <v>99072</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>108109</v>
+        <v>108108</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>101859</v>
+        <v>101860</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3045,7 +3045,7 @@
         <v>69559093</v>
       </c>
       <c r="B20" t="n">
-        <v>98933</v>
+        <v>98934</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>99072</v>
+        <v>99073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>101860</v>
+        <v>101861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3045,7 +3045,7 @@
         <v>69559093</v>
       </c>
       <c r="B20" t="n">
-        <v>98934</v>
+        <v>98937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>99073</v>
+        <v>99076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>108109</v>
+        <v>108107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>101861</v>
+        <v>101863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3257,7 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>108107</v>
+        <v>108108</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>101863</v>
+        <v>101864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3151,7 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>99076</v>
+        <v>99075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3045,7 +3045,7 @@
         <v>69559093</v>
       </c>
       <c r="B20" t="n">
-        <v>98937</v>
+        <v>98943</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>99075</v>
+        <v>99081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>108108</v>
+        <v>108114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>101864</v>
+        <v>101870</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3045,7 +3045,7 @@
         <v>69559093</v>
       </c>
       <c r="B20" t="n">
-        <v>98943</v>
+        <v>98946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>99081</v>
+        <v>99084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>108114</v>
+        <v>108120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>101870</v>
+        <v>101873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3045,7 +3045,7 @@
         <v>69559093</v>
       </c>
       <c r="B20" t="n">
-        <v>98946</v>
+        <v>98951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>99084</v>
+        <v>99089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>108120</v>
+        <v>108125</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>101873</v>
+        <v>101878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -3045,7 +3045,7 @@
         <v>69559093</v>
       </c>
       <c r="B20" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>69559092</v>
       </c>
       <c r="B21" t="n">
-        <v>99089</v>
+        <v>99091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>69559090</v>
       </c>
       <c r="B22" t="n">
-        <v>108125</v>
+        <v>108128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>69559088</v>
       </c>
       <c r="B23" t="n">
-        <v>101878</v>
+        <v>101881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3868566</v>
+        <v>215842</v>
       </c>
       <c r="B2" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221447</v>
+        <v>698</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
+          <t>Gentianella campestris var. campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -716,14 +711,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södermarken  (dellokal 2), Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>709520.8789539663</v>
+        <v>709548</v>
       </c>
       <c r="R2" t="n">
-        <v>6663496.405377786</v>
+        <v>6663459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Areal: 0,6 ha (1 x 30 m). Slåttertid v.33. Veg.höjd 20 cm</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,90 +764,66 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Slåtter</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Pettersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Pettersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13529070</v>
+        <v>222648</v>
       </c>
       <c r="B3" t="n">
-        <v>42542</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102923</v>
+        <v>698</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1760)</t>
-        </is>
-      </c>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergby slåtteräng, Upl</t>
+          <t>Bergby, 250 m S om badplats, 12J2c3248, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>709337.7075577129</v>
+        <v>709549</v>
       </c>
       <c r="R3" t="n">
-        <v>6663535.013661361</v>
+        <v>6663448</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,22 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2008-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2008-06-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2004-07-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>bladiga rosetter påvisades, säkert fler. Se M. Bergströms rapport: 62 blommande ex 2004-08-05. Rapportör Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,35 +868,39 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>öppen naturbetesmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri AB-län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>229025</v>
       </c>
       <c r="B4" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -978,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>709536.20681547</v>
+        <v>709536</v>
       </c>
       <c r="R4" t="n">
-        <v>6663473.757024803</v>
+        <v>6663474</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,19 +966,9 @@
           <t>2008-08-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1064,48 +1009,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13955731</v>
+        <v>232406</v>
       </c>
       <c r="B5" t="n">
-        <v>44327</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>201164</v>
+        <v>698</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>709408.3833814558</v>
+        <v>709536</v>
       </c>
       <c r="R5" t="n">
-        <v>6663455.962186529</v>
+        <v>6663455</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,22 +1084,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2008-07-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2008-07-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,70 +1103,65 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Längs stig i välhävdad slåtteräng.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan-Olov Björklund</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan-Olov Björklund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Inventering av fjärilar i Norrtälje kommun</t>
-        </is>
-      </c>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13955729</v>
+        <v>445032</v>
       </c>
       <c r="B6" t="n">
-        <v>42620</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>201122</v>
+        <v>1449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Almsnabbvinge</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Satyrium w-album</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Knoch, 1782)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1245,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>709408.3833814558</v>
+        <v>709429</v>
       </c>
       <c r="R6" t="n">
-        <v>6663455.962186529</v>
+        <v>6663436</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1275,22 +1200,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2008-07-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2008-07-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>grov uppskattning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,88 +1221,67 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Slåtteräng</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan-Olov Björklund</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan-Olov Björklund</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Inventering av fjärilar i Norrtälje kommun</t>
-        </is>
-      </c>
+          <t>Owe Rosengren, Ylva Trossvik</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13955730</v>
+        <v>6994678</v>
       </c>
       <c r="B7" t="n">
-        <v>44334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102021</v>
+        <v>1449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Knaben</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Häverö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>709408.3833814558</v>
+        <v>709479</v>
       </c>
       <c r="R7" t="n">
-        <v>6663455.962186529</v>
+        <v>6663409</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1406,22 +1305,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2008-07-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2008-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-06-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Medobs: Martin Bergström och Göran Andersson</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,92 +1326,64 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Slåtteräng</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan-Olov Björklund</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan-Olov Björklund</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering av fjärilar i Norrtälje kommun</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2461924</v>
+        <v>69559088</v>
       </c>
       <c r="B8" t="n">
-        <v>96274</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219792</v>
+        <v>1449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, SO om Bergby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>709428.565490454</v>
+        <v>709283</v>
       </c>
       <c r="R8" t="n">
-        <v>6663436.092162126</v>
+        <v>6663499</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1541,27 +1407,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2009-05-31</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2009-05-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>minst</t>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1576,27 +1432,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Ylva Trossvik</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>445032</v>
+        <v>102249726</v>
       </c>
       <c r="B9" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,51 +1459,62 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1449</v>
+        <v>102018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hällebräcka</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saxifraga osloënsis</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Knaben</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Bergby slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>709428.565490454</v>
+        <v>709338</v>
       </c>
       <c r="R9" t="n">
-        <v>6663436.092162126</v>
+        <v>6663535</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1672,27 +1538,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2009-05-31</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2009-05-31</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>grov uppskattning</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1701,72 +1562,59 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Ylva Trossvik</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14024015</v>
+        <v>13955730</v>
       </c>
       <c r="B10" t="n">
-        <v>42715</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102922</v>
+        <v>102021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ängsnätfjäril</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Melitaea cinxia</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1774,17 +1622,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergby slåtteräng, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>709337.7075577129</v>
+        <v>709408</v>
       </c>
       <c r="R10" t="n">
-        <v>6663535.013661361</v>
+        <v>6663456</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1808,22 +1656,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2009-06-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2008-07-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2009-06-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2008-07-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1834,83 +1672,98 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Jan-Olov Björklund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av fjärilar i Norrtälje kommun</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2622745</v>
+        <v>94837868</v>
       </c>
       <c r="B11" t="n">
-        <v>96231</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219795</v>
+        <v>102021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng (vid Trästabron), Upl</t>
+          <t>Bergby slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>709539.1520599296</v>
+        <v>709338</v>
       </c>
       <c r="R11" t="n">
-        <v>6663492.442392821</v>
+        <v>6663535</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1934,27 +1787,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2010-05-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2010-05-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Har precis börjat blomma.</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1963,60 +1801,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Slåtteräng.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2622748</v>
+        <v>14024015</v>
       </c>
       <c r="B12" t="n">
-        <v>96231</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219795</v>
+        <v>102922</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ängsnätfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Melitaea cinxia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2024,29 +1853,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Bergby slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>709519.1198826069</v>
+        <v>709338</v>
       </c>
       <c r="R12" t="n">
-        <v>6663483.292864323</v>
+        <v>6663535</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2070,22 +1904,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
+          <t>2009-06-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
+          <t>2009-06-27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2096,84 +1930,83 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Hävdad slåtteräng</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2466699</v>
+        <v>13529070</v>
       </c>
       <c r="B13" t="n">
-        <v>96274</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43251</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219792</v>
+        <v>102923</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Bergby slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>709513.2901272838</v>
+        <v>709338</v>
       </c>
       <c r="R13" t="n">
-        <v>6663462.441157303</v>
+        <v>6663535</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2197,110 +2030,107 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
+          <t>2008-06-15</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
+          <t>2008-06-15</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Hävdad slåtteräng</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6352562</v>
+        <v>94659950</v>
       </c>
       <c r="B14" t="n">
-        <v>98931</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43251</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224932</v>
+        <v>102923</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Lycaena hippothoe</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Bergsby, slåtteräng, norr om västra brofästet, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>709519.1198826069</v>
+        <v>709426</v>
       </c>
       <c r="R14" t="n">
-        <v>6663483.292864323</v>
+        <v>6663394</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2324,22 +2154,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2348,90 +2168,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Hävdad slåtteräng</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kristoffer Stighäll, Jan Edelsjö, Hans-Erik Wanntorp</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2464604</v>
+        <v>125294280</v>
       </c>
       <c r="B15" t="n">
-        <v>96274</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219792</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>709532.2215060837</v>
+        <v>709533</v>
       </c>
       <c r="R15" t="n">
-        <v>6663464.521300478</v>
+        <v>6663445</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2455,27 +2256,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 röd</t>
+          <t>Sjungande fågel.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,70 +2280,61 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Hävdad slåtteräng</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2466700</v>
+        <v>13955728</v>
       </c>
       <c r="B16" t="n">
-        <v>96274</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219792</v>
+        <v>201028</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2561,13 +2343,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>709478.6365687844</v>
+        <v>709408</v>
       </c>
       <c r="R16" t="n">
-        <v>6663445.952193902</v>
+        <v>6663456</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2591,27 +2373,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>6 röda. 4 gula</t>
+          <t>2008-07-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2625,81 +2392,95 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Hävdad slåtteräng</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan-Olov Björklund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Inventering av fjärilar i Norrtälje kommun</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2464605</v>
+        <v>94837975</v>
       </c>
       <c r="B17" t="n">
-        <v>96274</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219792</v>
+        <v>201028</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ochsenheimer, 1808)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Bergby slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>709524.1858285356</v>
+        <v>709338</v>
       </c>
       <c r="R17" t="n">
-        <v>6663473.572207352</v>
+        <v>6663535</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2723,114 +2504,106 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Hävdad slåtteräng</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2466701</v>
+        <v>94838012</v>
       </c>
       <c r="B18" t="n">
-        <v>96274</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43378</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219792</v>
+        <v>201075</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Bergby slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>709505.0838847874</v>
+        <v>709338</v>
       </c>
       <c r="R18" t="n">
-        <v>6663474.485218259</v>
+        <v>6663535</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2854,27 +2627,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>10 röda, 2 gula</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,75 +2641,62 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Hävdad slåtteräng</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2464603</v>
+        <v>13955729</v>
       </c>
       <c r="B19" t="n">
-        <v>96274</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219792</v>
+        <v>201122</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Almsnabbvinge</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza sambucina</t>
+          <t>Satyrium w-album</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Knoch, 1782)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2960,13 +2705,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>709541.6303102156</v>
+        <v>709408</v>
       </c>
       <c r="R19" t="n">
-        <v>6663466.559114364</v>
+        <v>6663456</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2990,27 +2735,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>6 röda 1 gul</t>
+          <t>2008-07-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3024,66 +2754,80 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Hävdad slåtteräng</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan-Olov Björklund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av fjärilar i Norrtälje kommun</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>69559093</v>
+        <v>13955731</v>
       </c>
       <c r="B20" t="n">
-        <v>98953</v>
+        <v>45042</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219795</v>
+        <v>201164</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>400 m SO om Bergby, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>709283</v>
+        <v>709408</v>
       </c>
       <c r="R20" t="n">
-        <v>6663499</v>
+        <v>6663456</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3107,17 +2851,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2008-07-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2008-07-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3128,68 +2867,90 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Jan-Olov Björklund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
+          <t>Jan-Olov Björklund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Upplands Flora 2010</t>
+          <t>Inventering av fjärilar i Norrtälje kommun</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>69559092</v>
+        <v>94659943</v>
       </c>
       <c r="B21" t="n">
-        <v>99091</v>
+        <v>45042</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>223621</v>
+        <v>201164</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>400 m SO om Bergby, Upl</t>
+          <t>Bergsby, slåtteräng, norr om västra brofästet, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>709283</v>
+        <v>709426</v>
       </c>
       <c r="R21" t="n">
-        <v>6663499</v>
+        <v>6663394</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3213,17 +2974,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2021-07-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3232,67 +2988,89 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Kristoffer Stighäll, Jan Edelsjö, Hans-Erik Wanntorp</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>69559090</v>
+        <v>94837952</v>
       </c>
       <c r="B22" t="n">
-        <v>108128</v>
+        <v>45042</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220103</v>
+        <v>201164</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Södermarken, SO om Bergby, Upl</t>
+          <t>Bergby slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>709283</v>
+        <v>709338</v>
       </c>
       <c r="R22" t="n">
-        <v>6663499</v>
+        <v>6663535</v>
       </c>
       <c r="S22" t="n">
         <v>100</v>
@@ -3319,17 +3097,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
+          <t>2021-07-11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>Fotade två. Kändes som det var många fler.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3338,70 +3116,81 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kenth Kärsrud</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Kenth Kärsrud</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>69559088</v>
+        <v>2457818</v>
       </c>
       <c r="B23" t="n">
-        <v>101881</v>
+        <v>99059</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1449</v>
+        <v>219792</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hällebräcka</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Saxifraga osloënsis</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Knaben</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Södermarken, SO om Bergby, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>709283</v>
+        <v>709529</v>
       </c>
       <c r="R23" t="n">
-        <v>6663499</v>
+        <v>6663448</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3425,17 +3214,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2008-05-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
+          <t>2008-05-25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>Slåtterhävdad</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3446,11 +3235,16 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3458,73 +3252,66 @@
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79177991</v>
+        <v>2461924</v>
       </c>
       <c r="B24" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>219792</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergbybadet, invid stigen vid gamla restaurengen, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>709473.7016206777</v>
+        <v>709429</v>
       </c>
       <c r="R24" t="n">
-        <v>6663523.744337799</v>
+        <v>6663436</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3548,22 +3335,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-07-23</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-07-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-05-31</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>minst</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3572,73 +3354,80 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Owe Rosengren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Owe Rosengren, Ylva Trossvik</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79861531</v>
+        <v>2464602</v>
       </c>
       <c r="B25" t="n">
-        <v>96313</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223609</v>
+        <v>219792</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>Dactylorhiza sambucina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södermarken, strax N om Trästabrons västra brofäste., Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>709492.997609152</v>
+        <v>709537</v>
       </c>
       <c r="R25" t="n">
-        <v>6663440.264511186</v>
+        <v>6663451</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3662,22 +3451,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>5 röda</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3686,43 +3470,37 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äng</t>
+          <t>Hävdad slåtteräng</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>85772856</v>
+        <v>2464603</v>
       </c>
       <c r="B26" t="n">
-        <v>96275</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3745,30 +3523,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>709547.2122279686</v>
+        <v>709542</v>
       </c>
       <c r="R26" t="n">
-        <v>6663465.375925212</v>
+        <v>6663467</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3792,27 +3572,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-05-21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-05-21</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Flertal hade inte klarat majs många frostnätter</t>
+          <t>6 röda 1 gul</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3821,34 +3591,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Hävdad slåtteräng</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>94837868</v>
+        <v>2464604</v>
       </c>
       <c r="B27" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3856,62 +3625,51 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102021</v>
+        <v>219792</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergby slåtteräng, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>709337.7075577129</v>
+        <v>709532</v>
       </c>
       <c r="R27" t="n">
-        <v>6663535.013661361</v>
+        <v>6663465</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3935,22 +3693,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 röd</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3959,34 +3712,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Hävdad slåtteräng</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>94837952</v>
+        <v>2466700</v>
       </c>
       <c r="B28" t="n">
-        <v>44328</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3994,62 +3746,51 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>201164</v>
+        <v>219792</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergby slåtteräng, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>709337.7075577129</v>
+        <v>709479</v>
       </c>
       <c r="R28" t="n">
-        <v>6663535.013661361</v>
+        <v>6663446</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4073,27 +3814,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Fotade två. Kändes som det var många fler.</t>
+          <t>6 röda. 4 gula</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4102,38 +3833,37 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Hävdad slåtteräng</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101057234</v>
+        <v>2466701</v>
       </c>
       <c r="B29" t="n">
-        <v>96275</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4156,7 +3886,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4169,20 +3899,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trästabron, Norrtälje, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>709555.5363179486</v>
+        <v>709505</v>
       </c>
       <c r="R29" t="n">
-        <v>6663468.853356026</v>
+        <v>6663474</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4206,22 +3935,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:16</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:16</t>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>10 röda, 2 gula</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4232,31 +3956,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Hävdad slåtteräng</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Margaux Boeraeve</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Margaux Boeraeve, Ward Tamsyn, Flor Rhebergen</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102249726</v>
+        <v>85772856</v>
       </c>
       <c r="B30" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4264,62 +3988,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102018</v>
+        <v>219792</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergby slåtteräng, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>709337.7075577129</v>
+        <v>709547</v>
       </c>
       <c r="R30" t="n">
-        <v>6663535.013661361</v>
+        <v>6663465</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4343,22 +4054,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2020-05-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2020-05-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flertal hade inte klarat majs många frostnätter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4374,77 +4080,75 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Sten Pettersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kenth Kärsrud</t>
+          <t>Sten Pettersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111491247</v>
+        <v>101057234</v>
       </c>
       <c r="B31" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219862</v>
+        <v>219792</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergbybadet, invid stigen vid gamla restaurengen, Upl</t>
+          <t>Trästabron, Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>709473.7016206777</v>
+        <v>709556</v>
       </c>
       <c r="R31" t="n">
-        <v>6663523.744337799</v>
+        <v>6663469</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4468,22 +4172,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4492,59 +4196,62 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Margaux Boeraeve</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Margaux Boeraeve, Ward Tamsyn, Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111503017</v>
+        <v>2622745</v>
       </c>
       <c r="B32" t="n">
-        <v>99605</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99017</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221333</v>
+        <v>219795</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4552,17 +4259,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Södermarken, V Trästabron, Upl</t>
+          <t>Södermarkens slåtteräng (vid Trästabron), Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>709538.274674179</v>
+        <v>709539</v>
       </c>
       <c r="R32" t="n">
-        <v>6663463.865436872</v>
+        <v>6663492</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4586,22 +4293,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Har precis börjat blomma.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4615,28 +4317,28 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Naturbetesmark</t>
+          <t>Slåtteräng.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125294301</v>
+        <v>2622748</v>
       </c>
       <c r="B33" t="n">
-        <v>105270</v>
+        <v>99017</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4644,24 +4346,33 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221141</v>
+        <v>219795</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -4669,17 +4380,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>709511</v>
+        <v>709519</v>
       </c>
       <c r="R33" t="n">
-        <v>6663457</v>
+        <v>6663483</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4703,12 +4414,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2010-06-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4722,32 +4433,28 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Hävdad slåtteräng</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125294338</v>
+        <v>69559093</v>
       </c>
       <c r="B34" t="n">
-        <v>100516</v>
+        <v>99094</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4755,42 +4462,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>219795</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>400 m SO om Bergby, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>709424</v>
+        <v>709283</v>
       </c>
       <c r="R34" t="n">
-        <v>6663425</v>
+        <v>6663499</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4814,17 +4516,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Lite skuggigare plats.</t>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4835,57 +4537,52 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Slåtteräng</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Kärlväxtinventering Södermarken</t>
+          <t>Upplands Flora 2010</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125294304</v>
+        <v>67270586</v>
       </c>
       <c r="B35" t="n">
-        <v>98961</v>
+        <v>99096</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222295</v>
+        <v>219798</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4896,14 +4593,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Trästabrons V fäste, N om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>709463</v>
+        <v>709394</v>
       </c>
       <c r="R35" t="n">
-        <v>6663432</v>
+        <v>6663409</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4930,12 +4627,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2017-08-13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2017-08-13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Sex plantor samt en avklippt.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4949,7 +4651,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Busksnår</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4960,60 +4662,71 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Jan Yngve Andersson, solveig raaschou, Ann Sjölander, Linnea Glav Lundin, Bo Reichenberg, Linda Irebrand, Eva Grönlund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>Kärlväxtinventering Södermarken</t>
+          <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127633119</v>
+        <v>72399572</v>
       </c>
       <c r="B36" t="n">
-        <v>104441</v>
+        <v>99096</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224416</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Parkeringen till Bergbybadet vid vägbommen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>709458</v>
+        <v>709365</v>
       </c>
       <c r="R36" t="n">
-        <v>6663422</v>
+        <v>6663404</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5037,12 +4750,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2018-07-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5051,30 +4764,3738 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Slåtteräng</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
+          <t>Sten Pettersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sten Pettersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>79177991</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bergbybadet, invid stigen vid gamla restaurengen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>709474</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6663524</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2019-07-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2019-07-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sten Pettersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sten Pettersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2296736</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>709437</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6663387</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2011-06-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2011-06-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Grov skattning, spridd på flera ställen i slåtterängen.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Öppen slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126341435</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Södermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>709448</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6663394</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr">
+      <c r="AY39" t="inlineStr">
         <is>
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127633124</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Södermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>709461</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6663400</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Totalt fyra plantor. Nära utegymmet I riktning mot landsvägen.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125294345</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>709379</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6663402</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>111491247</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99141</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bergbybadet, invid stigen vid gamla restaurengen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>709474</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6663524</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sten Pettersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sten Pettersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>69559091</v>
+      </c>
+      <c r="B43" t="n">
+        <v>107943</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Södermarken, SO om Bergby, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>709283</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6663499</v>
+      </c>
+      <c r="S43" t="n">
+        <v>100</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>69559090</v>
+      </c>
+      <c r="B44" t="n">
+        <v>108275</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Södermarken, SO om Bergby, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>709283</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6663499</v>
+      </c>
+      <c r="S44" t="n">
+        <v>100</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3363680</v>
+      </c>
+      <c r="B45" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>709548</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6663459</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>117241732</v>
+      </c>
+      <c r="B46" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Södermarken vid Trästabrons västra fäste, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>709461</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6663410</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Äng (har slåttrats tidigare)</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125294301</v>
+      </c>
+      <c r="B47" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>709511</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6663457</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125294315</v>
+      </c>
+      <c r="B48" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>709464</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6663393</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3980317</v>
+      </c>
+      <c r="B49" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>709548</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6663459</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>111503017</v>
+      </c>
+      <c r="B50" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Södermarken, V Trästabron, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>709538</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6663464</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3848128</v>
+      </c>
+      <c r="B51" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>709548</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6663459</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>1994-05-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>1994-05-09</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Ohävdad slåtteräng vid stigkorsning</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3861369</v>
+      </c>
+      <c r="B52" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Södermarken, Häverö, Norrtälje, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>709541</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6663457</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2003-07-15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2003-07-15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Lieslåtter 2001 - 10 ex</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3868565</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Södermarken  (dellokal 1), Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>709537</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6663446</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Areal: 0,6 ha (22 x 6 m). Slåttertid v.33. Veg.höjd 20 cm. Sköts fr.o.m. 2002 av Stiftelsen Norrtälje Naturvårdsfond.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Slåtter</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3868566</v>
+      </c>
+      <c r="B54" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Södermarken  (dellokal 2), Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>709521</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6663496</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Areal: 0,6 ha (1 x 30 m). Slåttertid v.33. Veg.höjd 20 cm</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Slåtter</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Maria Pettersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4532115</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>709548</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6663459</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4418368</v>
+      </c>
+      <c r="B56" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>709548</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6663459</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4427038</v>
+      </c>
+      <c r="B57" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng (vid Trästabron), Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>709424</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6663393</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2010-05-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2010-05-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Har precis börjat blomma.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Friskäng, slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>111503016</v>
+      </c>
+      <c r="B58" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Södermarken, V Trästabron, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>709543</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6663463</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127633110</v>
+      </c>
+      <c r="B59" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Södermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>709547</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6663458</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125294304</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>709463</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6663432</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125294346</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>709383</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6663405</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125294338</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>709424</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6663425</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Lite skuggigare plats.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>79861531</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Södermarken, strax N om Trästabrons västra brofäste., Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>709493</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6663440</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Äng</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5994122</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99121</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223614</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vanlig brudsporre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Södermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>709464</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6663397</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2009-06-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2009-06-26</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>3 smågrupper med 5, 2, och 5 ex</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>69559092</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99232</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>400 m SO om Bergby, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>709283</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6663499</v>
+      </c>
+      <c r="S65" t="n">
+        <v>100</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2665273</v>
+      </c>
+      <c r="B66" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>709548</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6663459</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>1998-08-05</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>111503012</v>
+      </c>
+      <c r="B67" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Södermarken, V Trästabron, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>709560</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6663464</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Naturbetesmark</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127633113</v>
+      </c>
+      <c r="B68" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Södermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>709502</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6663436</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127633119</v>
+      </c>
+      <c r="B69" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Södermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>709458</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6663422</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6352562</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101746</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>709519</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6663483</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Hävdad slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5253,10 +5253,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125294345</v>
+        <v>134603581</v>
       </c>
       <c r="B41" t="n">
-        <v>99142</v>
+        <v>99197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5264,39 +5264,48 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarken vid Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>709379</v>
+        <v>709542</v>
       </c>
       <c r="R41" t="n">
-        <v>6663402</v>
+        <v>6663459</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5323,12 +5332,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5356,18 +5365,14 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111491247</v>
+        <v>134603585</v>
       </c>
       <c r="B42" t="n">
-        <v>99141</v>
+        <v>99197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5375,46 +5380,48 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219862</v>
+        <v>219811</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergbybadet, invid stigen vid gamla restaurengen, Upl</t>
+          <t>Södermarken vid Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>709474</v>
+        <v>709452</v>
       </c>
       <c r="R42" t="n">
-        <v>6663524</v>
+        <v>6663396</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5441,12 +5448,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5455,29 +5462,33 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>69559091</v>
+        <v>125294345</v>
       </c>
       <c r="B43" t="n">
-        <v>107943</v>
+        <v>99142</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5485,37 +5496,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219933</v>
+        <v>219847</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södermarken, SO om Bergby, Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>709283</v>
+        <v>709379</v>
       </c>
       <c r="R43" t="n">
-        <v>6663499</v>
+        <v>6663402</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5539,17 +5555,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5560,68 +5571,85 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Upplands Flora 2010</t>
+          <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>69559090</v>
+        <v>111491247</v>
       </c>
       <c r="B44" t="n">
-        <v>108275</v>
+        <v>99141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220103</v>
+        <v>219862</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södermarken, SO om Bergby, Upl</t>
+          <t>Bergbybadet, invid stigen vid gamla restaurengen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>709283</v>
+        <v>709474</v>
       </c>
       <c r="R44" t="n">
-        <v>6663499</v>
+        <v>6663524</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5645,17 +5673,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5664,32 +5687,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Sten Pettersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Sten Pettersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3363680</v>
+        <v>69559091</v>
       </c>
       <c r="B45" t="n">
-        <v>106156</v>
+        <v>107943</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5697,37 +5717,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221141</v>
+        <v>219933</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, SO om Bergby, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>709548</v>
+        <v>709283</v>
       </c>
       <c r="R45" t="n">
-        <v>6663459</v>
+        <v>6663499</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5751,12 +5771,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5767,74 +5792,68 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117241732</v>
+        <v>69559090</v>
       </c>
       <c r="B46" t="n">
-        <v>106156</v>
+        <v>108275</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Södermarken vid Trästabrons västra fäste, Upl</t>
+          <t>Södermarken, SO om Bergby, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>709461</v>
+        <v>709283</v>
       </c>
       <c r="R46" t="n">
-        <v>6663410</v>
+        <v>6663499</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5858,12 +5877,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5874,28 +5898,27 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Äng (har slåttrats tidigare)</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125294301</v>
+        <v>3363680</v>
       </c>
       <c r="B47" t="n">
         <v>106156</v>
@@ -5924,21 +5947,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>709511</v>
+        <v>709548</v>
       </c>
       <c r="R47" t="n">
-        <v>6663457</v>
+        <v>6663459</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5965,12 +5983,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5984,29 +6002,25 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125294315</v>
+        <v>117241732</v>
       </c>
       <c r="B48" t="n">
         <v>106156</v>
@@ -6042,14 +6056,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarken vid Trästabrons västra fäste, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>709464</v>
+        <v>709461</v>
       </c>
       <c r="R48" t="n">
-        <v>6663393</v>
+        <v>6663410</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6076,12 +6090,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6095,7 +6109,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Äng (har slåttrats tidigare)</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6109,35 +6123,31 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3980317</v>
+        <v>125294301</v>
       </c>
       <c r="B49" t="n">
-        <v>102443</v>
+        <v>106156</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221333</v>
+        <v>221141</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6146,16 +6156,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>709548</v>
+        <v>709511</v>
       </c>
       <c r="R49" t="n">
-        <v>6663459</v>
+        <v>6663457</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6182,12 +6197,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6201,45 +6216,49 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111503017</v>
+        <v>125294315</v>
       </c>
       <c r="B50" t="n">
-        <v>102443</v>
+        <v>106156</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221333</v>
+        <v>221141</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6255,14 +6274,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Södermarken, V Trästabron, Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>709538</v>
+        <v>709464</v>
       </c>
       <c r="R50" t="n">
-        <v>6663464</v>
+        <v>6663393</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6289,12 +6308,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6308,7 +6327,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Naturbetesmark</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6322,49 +6341,43 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3848128</v>
+        <v>3980317</v>
       </c>
       <c r="B51" t="n">
-        <v>106414</v>
+        <v>102443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221447</v>
+        <v>221333</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Södermarkens slåtteräng, Upl</t>
@@ -6377,7 +6390,7 @@
         <v>6663459</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6401,12 +6414,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>1994-05-09</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1994-05-09</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6420,7 +6433,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Ohävdad slåtteräng vid stigkorsning</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6438,41 +6451,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3861369</v>
+        <v>111503017</v>
       </c>
       <c r="B52" t="n">
-        <v>106414</v>
+        <v>102443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221447</v>
+        <v>221333</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Södermarken, Häverö, Norrtälje, Upl</t>
+          <t>Södermarken, V Trästabron, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>709541</v>
+        <v>709538</v>
       </c>
       <c r="R52" t="n">
-        <v>6663457</v>
+        <v>6663464</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6499,12 +6521,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2003-07-15</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2003-07-15</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6518,25 +6540,25 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Lieslåtter 2001 - 10 ex</t>
+          <t>Naturbetesmark</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3868565</v>
+        <v>3848128</v>
       </c>
       <c r="B53" t="n">
         <v>106414</v>
@@ -6562,7 +6584,7 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6570,19 +6592,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södermarken  (dellokal 1), Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>709537</v>
+        <v>709548</v>
       </c>
       <c r="R53" t="n">
-        <v>6663446</v>
+        <v>6663459</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6606,17 +6633,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
+          <t>1994-05-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Areal: 0,6 ha (22 x 6 m). Slåttertid v.33. Veg.höjd 20 cm. Sköts fr.o.m. 2002 av Stiftelsen Norrtälje Naturvårdsfond.</t>
+          <t>1994-05-09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6630,25 +6652,25 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Slåtter</t>
+          <t>Ohävdad slåtteräng vid stigkorsning</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Maria Pettersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Maria Pettersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3868566</v>
+        <v>3861369</v>
       </c>
       <c r="B54" t="n">
         <v>106414</v>
@@ -6672,26 +6694,17 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södermarken  (dellokal 2), Upl</t>
+          <t>Södermarken, Häverö, Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>709521</v>
+        <v>709541</v>
       </c>
       <c r="R54" t="n">
-        <v>6663496</v>
+        <v>6663457</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6718,17 +6731,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
+          <t>2003-07-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Areal: 0,6 ha (1 x 30 m). Slåttertid v.33. Veg.höjd 20 cm</t>
+          <t>2003-07-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6742,55 +6750,51 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Slåtter</t>
+          <t>Lieslåtter 2001 - 10 ex</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Maria Pettersson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Maria Pettersson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4532115</v>
+        <v>3868565</v>
       </c>
       <c r="B55" t="n">
-        <v>98050</v>
+        <v>106414</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222112</v>
+        <v>221447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6800,14 +6804,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken  (dellokal 1), Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>709548</v>
+        <v>709537</v>
       </c>
       <c r="R55" t="n">
-        <v>6663459</v>
+        <v>6663446</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6834,12 +6838,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-08-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Areal: 0,6 ha (22 x 6 m). Slåttertid v.33. Veg.höjd 20 cm. Sköts fr.o.m. 2002 av Stiftelsen Norrtälje Naturvårdsfond.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6853,63 +6862,68 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+          <t>Slåtter</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4418368</v>
+        <v>3868566</v>
       </c>
       <c r="B56" t="n">
-        <v>102560</v>
+        <v>106414</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222133</v>
+        <v>221447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken  (dellokal 2), Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>709548</v>
+        <v>709521</v>
       </c>
       <c r="R56" t="n">
-        <v>6663459</v>
+        <v>6663496</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6936,12 +6950,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-08-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Areal: 0,6 ha (1 x 30 m). Slåttertid v.33. Veg.höjd 20 cm</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6955,28 +6974,28 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+          <t>Slåtter</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4427038</v>
+        <v>4532115</v>
       </c>
       <c r="B57" t="n">
-        <v>102560</v>
+        <v>98050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6984,47 +7003,46 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222133</v>
+        <v>222112</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng (vid Trästabron), Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>709424</v>
+        <v>709548</v>
       </c>
       <c r="R57" t="n">
-        <v>6663393</v>
+        <v>6663459</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7048,17 +7066,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2010-05-24</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2010-05-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Har precis börjat blomma.</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7072,25 +7085,25 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Friskäng, slåtteräng</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>111503016</v>
+        <v>4418368</v>
       </c>
       <c r="B58" t="n">
         <v>102560</v>
@@ -7119,21 +7132,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Södermarken, V Trästabron, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>709543</v>
+        <v>709548</v>
       </c>
       <c r="R58" t="n">
-        <v>6663463</v>
+        <v>6663459</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7160,12 +7168,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7179,25 +7187,25 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Naturbetesmark</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127633110</v>
+        <v>4427038</v>
       </c>
       <c r="B59" t="n">
         <v>102560</v>
@@ -7226,6 +7234,11 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -7233,17 +7246,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Södermarkens slåtteräng (vid Trästabron), Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>709547</v>
+        <v>709424</v>
       </c>
       <c r="R59" t="n">
-        <v>6663458</v>
+        <v>6663393</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7267,12 +7280,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2010-05-24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2010-05-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Har precis börjat blomma.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7286,32 +7304,28 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Friskäng, slåtteräng</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125294304</v>
+        <v>111503016</v>
       </c>
       <c r="B60" t="n">
-        <v>99754</v>
+        <v>102560</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7319,21 +7333,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222295</v>
+        <v>222133</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7344,14 +7358,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarken, V Trästabron, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>709463</v>
+        <v>709543</v>
       </c>
       <c r="R60" t="n">
-        <v>6663432</v>
+        <v>6663463</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7378,12 +7392,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7397,7 +7411,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Naturbetesmark</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7411,18 +7425,14 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125294346</v>
+        <v>127633110</v>
       </c>
       <c r="B61" t="n">
-        <v>99754</v>
+        <v>102560</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7430,21 +7440,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222295</v>
+        <v>222133</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7455,14 +7465,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>709383</v>
+        <v>709547</v>
       </c>
       <c r="R61" t="n">
-        <v>6663405</v>
+        <v>6663458</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7489,12 +7499,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7530,38 +7540,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125294338</v>
+        <v>125294304</v>
       </c>
       <c r="B62" t="n">
-        <v>101326</v>
+        <v>99754</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>222295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7570,10 +7580,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>709424</v>
+        <v>709463</v>
       </c>
       <c r="R62" t="n">
-        <v>6663425</v>
+        <v>6663432</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7606,11 +7616,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Lite skuggigare plats.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7646,46 +7651,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>79861531</v>
+        <v>125294346</v>
       </c>
       <c r="B63" t="n">
-        <v>99097</v>
+        <v>99754</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>223609</v>
+        <v>222295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Södermarken, strax N om Trästabrons västra brofäste., Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>709493</v>
+        <v>709383</v>
       </c>
       <c r="R63" t="n">
-        <v>6663440</v>
+        <v>6663405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7712,12 +7721,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7726,13 +7735,12 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Äng</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7746,14 +7754,18 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>5994122</v>
+        <v>125294338</v>
       </c>
       <c r="B64" t="n">
-        <v>99121</v>
+        <v>101326</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7761,39 +7773,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>223614</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>709464</v>
+        <v>709424</v>
       </c>
       <c r="R64" t="n">
-        <v>6663397</v>
+        <v>6663425</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7820,17 +7832,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2009-06-26</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2009-06-26</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>3 smågrupper med 5, 2, och 5 ex</t>
+          <t>Lite skuggigare plats.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7844,28 +7856,32 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>slåtteräng</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>69559092</v>
+        <v>79861531</v>
       </c>
       <c r="B65" t="n">
-        <v>99232</v>
+        <v>99097</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7873,37 +7889,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223621</v>
+        <v>223609</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>400 m SO om Bergby, Upl</t>
+          <t>Södermarken, strax N om Trästabrons västra brofäste., Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>709283</v>
+        <v>709493</v>
       </c>
       <c r="R65" t="n">
-        <v>6663499</v>
+        <v>6663440</v>
       </c>
       <c r="S65" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7927,17 +7944,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7946,63 +7958,74 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Äng</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2665273</v>
+        <v>5994122</v>
       </c>
       <c r="B66" t="n">
-        <v>104641</v>
+        <v>99121</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>224416</v>
+        <v>223614</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>709548</v>
+        <v>709464</v>
       </c>
       <c r="R66" t="n">
-        <v>6663459</v>
+        <v>6663397</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8029,12 +8052,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2009-06-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2009-06-26</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>3 smågrupper med 5, 2, och 5 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8048,67 +8076,66 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+          <t>slåtteräng</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>111503012</v>
+        <v>69559092</v>
       </c>
       <c r="B67" t="n">
-        <v>104641</v>
+        <v>99232</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>224416</v>
+        <v>223621</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Södermarken, V Trästabron, Upl</t>
+          <t>400 m SO om Bergby, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>709560</v>
+        <v>709283</v>
       </c>
       <c r="R67" t="n">
-        <v>6663464</v>
+        <v>6663499</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8132,12 +8159,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8148,28 +8180,27 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Naturbetesmark</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127633113</v>
+        <v>2665273</v>
       </c>
       <c r="B68" t="n">
         <v>104641</v>
@@ -8194,24 +8225,16 @@
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>709502</v>
+        <v>709548</v>
       </c>
       <c r="R68" t="n">
-        <v>6663436</v>
+        <v>6663459</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8238,12 +8261,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8252,38 +8275,33 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127633119</v>
+        <v>111503012</v>
       </c>
       <c r="B69" t="n">
-        <v>104640</v>
+        <v>104641</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8312,14 +8330,14 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Södermarken, V Trästabron, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>709458</v>
+        <v>709560</v>
       </c>
       <c r="R69" t="n">
-        <v>6663422</v>
+        <v>6663464</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8346,12 +8364,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8365,7 +8383,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Naturbetesmark</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8379,18 +8397,14 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6352562</v>
+        <v>127633113</v>
       </c>
       <c r="B70" t="n">
-        <v>101746</v>
+        <v>104641</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8398,47 +8412,41 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>224932</v>
+        <v>224416</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>709519</v>
+        <v>709502</v>
       </c>
       <c r="R70" t="n">
-        <v>6663483</v>
+        <v>6663436</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8462,12 +8470,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8476,26 +8484,250 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Hävdad slåtteräng</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>127633119</v>
+      </c>
+      <c r="B71" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Södermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>709458</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6663422</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>6352562</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101746</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>709519</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6663483</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Hävdad slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
+      <c r="AX72" t="inlineStr">
         <is>
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/215842</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/222648</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/229025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/232406</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/445032</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6994678</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69559088</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102249726</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
           <t>Inventering av fjärilar i Norrtälje kommun</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13955730</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1817,6 +1867,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94837868</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1943,6 +1998,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14024015</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2069,6 +2129,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13529070</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2184,6 +2249,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94659950</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294280</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2411,6 +2486,11 @@
           <t>Inventering av fjärilar i Norrtälje kommun</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13955728</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2534,6 +2614,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94837975</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2657,6 +2742,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94838012</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2773,6 +2863,11 @@
           <t>Inventering av fjärilar i Norrtälje kommun</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13955729</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2889,6 +2984,11 @@
           <t>Inventering av fjärilar i Norrtälje kommun</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13955731</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3004,6 +3104,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94659943</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3132,6 +3237,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94837952</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3253,6 +3363,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2457818</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3369,6 +3484,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2461924</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3490,6 +3610,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2464602</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3611,6 +3736,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2464603</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3732,6 +3862,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2464604</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3853,6 +3988,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2466700</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3974,6 +4114,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2466701</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4089,6 +4234,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85772856</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4211,6 +4361,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101057234</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4332,6 +4487,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2622745</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4448,6 +4608,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2622748</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4554,6 +4719,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69559093</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4670,6 +4840,11 @@
           <t>BSIS - Floraväkteri-exkursion</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67270586</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4780,6 +4955,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72399572</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4890,6 +5070,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79177991</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5011,6 +5196,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2296736</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5134,6 +5324,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126341435</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5250,6 +5445,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127633124</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5366,6 +5566,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134603581</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5482,6 +5687,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134603585</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5593,6 +5803,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294345</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5703,6 +5918,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491247</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5809,6 +6029,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69559091</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5915,6 +6140,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69559090</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6017,6 +6247,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3363680</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6124,6 +6359,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117241732</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6235,6 +6475,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294301</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6346,6 +6591,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294315</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6448,6 +6698,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3980317</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6555,6 +6810,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111503017</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6667,6 +6927,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3848128</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6765,6 +7030,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3861369</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6877,6 +7147,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3868565</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6989,6 +7264,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3868566</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7100,6 +7380,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4532115</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7202,6 +7487,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4418368</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7319,6 +7609,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4427038</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7426,6 +7721,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111503016</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7537,6 +7837,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127633110</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7648,6 +7953,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294304</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7759,6 +8069,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294346</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7875,6 +8190,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125294338</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7979,6 +8299,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79861531</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8091,6 +8416,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5994122</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8197,6 +8527,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69559092</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8295,6 +8630,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2665273</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8398,6 +8738,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111503012</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8509,6 +8854,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127633113</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8616,6 +8966,11 @@
           <t>Kärlväxtinventering Södermarken</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127633119</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8728,8 +9083,86 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6352562</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ72"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5078,10 +5078,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2296736</v>
+        <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99120</v>
+        <v>99272</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,26 +5089,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219811</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5121,19 +5121,20 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken intill parkeringen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>709437</v>
+        <v>709363</v>
       </c>
       <c r="R38" t="n">
-        <v>6663387</v>
+        <v>6663405</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5157,17 +5158,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2011-06-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2011-06-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Grov skattning, spridd på flera ställen i slåtterängen.</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5176,35 +5172,36 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Öppen slåtteräng</t>
+          <t>Vägkant, artrik</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Jan Yngve Andersson, Patrik Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2296736</t>
+          <t>https://artportalen.se/Sighting/136153629</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126341435</v>
+        <v>2296736</v>
       </c>
       <c r="B39" t="n">
         <v>99120</v>
@@ -5234,7 +5231,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5247,21 +5244,19 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>709448</v>
+        <v>709437</v>
       </c>
       <c r="R39" t="n">
-        <v>6663394</v>
+        <v>6663387</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5285,12 +5280,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2011-06-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2011-06-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Grov skattning, spridd på flera ställen i slåtterängen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5299,40 +5299,35 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Öppen slåtteräng</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126341435</t>
+          <t>https://artportalen.se/Sighting/2296736</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127633124</v>
+        <v>126341435</v>
       </c>
       <c r="B40" t="n">
         <v>99120</v>
@@ -5360,22 +5355,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>709461</v>
+        <v>709448</v>
       </c>
       <c r="R40" t="n">
-        <v>6663400</v>
+        <v>6663394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5402,17 +5408,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Totalt fyra plantor. Nära utegymmet I riktning mot landsvägen.</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5421,6 +5422,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5447,16 +5449,16 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127633124</t>
+          <t>https://artportalen.se/Sighting/126341435</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134603581</v>
+        <v>127633124</v>
       </c>
       <c r="B41" t="n">
-        <v>99197</v>
+        <v>99120</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5481,31 +5483,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södermarken vid Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>709542</v>
+        <v>709461</v>
       </c>
       <c r="R41" t="n">
-        <v>6663459</v>
+        <v>6663400</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5532,12 +5525,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Totalt fyra plantor. Nära utegymmet I riktning mot landsvägen.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5565,16 +5563,20 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134603581</t>
+          <t>https://artportalen.se/Sighting/127633124</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134603585</v>
+        <v>134603581</v>
       </c>
       <c r="B42" t="n">
         <v>99197</v>
@@ -5623,10 +5625,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>709452</v>
+        <v>709542</v>
       </c>
       <c r="R42" t="n">
-        <v>6663396</v>
+        <v>6663459</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5689,16 +5691,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134603585</t>
+          <t>https://artportalen.se/Sighting/134603581</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125294345</v>
+        <v>134603585</v>
       </c>
       <c r="B43" t="n">
-        <v>99142</v>
+        <v>99197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5706,39 +5708,48 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarken vid Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>709379</v>
+        <v>709452</v>
       </c>
       <c r="R43" t="n">
-        <v>6663402</v>
+        <v>6663396</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5765,12 +5776,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5798,23 +5809,19 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125294345</t>
+          <t>https://artportalen.se/Sighting/134603585</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111491247</v>
+        <v>125294345</v>
       </c>
       <c r="B44" t="n">
-        <v>99141</v>
+        <v>99142</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5822,46 +5829,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergbybadet, invid stigen vid gamla restaurengen, Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>709474</v>
+        <v>709379</v>
       </c>
       <c r="R44" t="n">
-        <v>6663524</v>
+        <v>6663402</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5888,12 +5888,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5902,34 +5902,42 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Slåtteräng</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sten Pettersson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111491247</t>
+          <t>https://artportalen.se/Sighting/125294345</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>69559091</v>
+        <v>111491247</v>
       </c>
       <c r="B45" t="n">
-        <v>107943</v>
+        <v>99141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5937,37 +5945,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219933</v>
+        <v>219862</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Södermarken, SO om Bergby, Upl</t>
+          <t>Bergbybadet, invid stigen vid gamla restaurengen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>709283</v>
+        <v>709474</v>
       </c>
       <c r="R45" t="n">
-        <v>6663499</v>
+        <v>6663524</v>
       </c>
       <c r="S45" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5991,17 +6011,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6010,59 +6025,56 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Sten Pettersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Sten Pettersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69559091</t>
+          <t>https://artportalen.se/Sighting/111491247</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>69559090</v>
+        <v>69559091</v>
       </c>
       <c r="B46" t="n">
-        <v>108275</v>
+        <v>107943</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220103</v>
+        <v>219933</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6142,54 +6154,54 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69559090</t>
+          <t>https://artportalen.se/Sighting/69559091</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3363680</v>
+        <v>69559090</v>
       </c>
       <c r="B47" t="n">
-        <v>106156</v>
+        <v>108275</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, SO om Bergby, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>709548</v>
+        <v>709283</v>
       </c>
       <c r="R47" t="n">
-        <v>6663459</v>
+        <v>6663499</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6213,12 +6225,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6229,33 +6246,32 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3363680</t>
+          <t>https://artportalen.se/Sighting/69559090</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117241732</v>
+        <v>3363680</v>
       </c>
       <c r="B48" t="n">
         <v>106156</v>
@@ -6284,21 +6300,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Södermarken vid Trästabrons västra fäste, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>709461</v>
+        <v>709548</v>
       </c>
       <c r="R48" t="n">
-        <v>6663410</v>
+        <v>6663459</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6325,12 +6336,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6344,30 +6355,30 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äng (har slåttrats tidigare)</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117241732</t>
+          <t>https://artportalen.se/Sighting/3363680</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125294301</v>
+        <v>117241732</v>
       </c>
       <c r="B49" t="n">
         <v>106156</v>
@@ -6403,14 +6414,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarken vid Trästabrons västra fäste, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>709511</v>
+        <v>709461</v>
       </c>
       <c r="R49" t="n">
-        <v>6663457</v>
+        <v>6663410</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6437,12 +6448,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6456,7 +6467,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Äng (har slåttrats tidigare)</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6470,20 +6481,16 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+      <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125294301</t>
+          <t>https://artportalen.se/Sighting/117241732</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125294315</v>
+        <v>125294301</v>
       </c>
       <c r="B50" t="n">
         <v>106156</v>
@@ -6523,10 +6530,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>709464</v>
+        <v>709511</v>
       </c>
       <c r="R50" t="n">
-        <v>6663393</v>
+        <v>6663457</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6593,33 +6600,33 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125294315</t>
+          <t>https://artportalen.se/Sighting/125294301</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3980317</v>
+        <v>125294315</v>
       </c>
       <c r="B51" t="n">
-        <v>102443</v>
+        <v>106156</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221333</v>
+        <v>221141</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6628,16 +6635,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>709548</v>
+        <v>709464</v>
       </c>
       <c r="R51" t="n">
-        <v>6663459</v>
+        <v>6663393</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6664,12 +6676,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6683,30 +6695,34 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3980317</t>
+          <t>https://artportalen.se/Sighting/125294315</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>111503017</v>
+        <v>3980317</v>
       </c>
       <c r="B52" t="n">
         <v>102443</v>
@@ -6735,21 +6751,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Södermarken, V Trästabron, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>709538</v>
+        <v>709548</v>
       </c>
       <c r="R52" t="n">
-        <v>6663464</v>
+        <v>6663459</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6776,12 +6787,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6795,81 +6806,76 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Naturbetesmark</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111503017</t>
+          <t>https://artportalen.se/Sighting/3980317</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3848128</v>
+        <v>111503017</v>
       </c>
       <c r="B53" t="n">
-        <v>106414</v>
+        <v>102443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221447</v>
+        <v>221333</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, V Trästabron, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>709548</v>
+        <v>709538</v>
       </c>
       <c r="R53" t="n">
-        <v>6663459</v>
+        <v>6663464</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6893,12 +6899,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1994-05-09</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>1994-05-09</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6912,30 +6918,30 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Ohävdad slåtteräng vid stigkorsning</t>
+          <t>Naturbetesmark</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3848128</t>
+          <t>https://artportalen.se/Sighting/111503017</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3861369</v>
+        <v>3848128</v>
       </c>
       <c r="B54" t="n">
         <v>106414</v>
@@ -6959,20 +6965,34 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södermarken, Häverö, Norrtälje, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>709541</v>
+        <v>709548</v>
       </c>
       <c r="R54" t="n">
-        <v>6663457</v>
+        <v>6663459</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6996,12 +7016,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2003-07-15</t>
+          <t>1994-05-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2003-07-15</t>
+          <t>1994-05-09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7015,30 +7035,30 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Lieslåtter 2001 - 10 ex</t>
+          <t>Ohävdad slåtteräng vid stigkorsning</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3861369</t>
+          <t>https://artportalen.se/Sighting/3848128</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3868565</v>
+        <v>3861369</v>
       </c>
       <c r="B55" t="n">
         <v>106414</v>
@@ -7062,26 +7082,17 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Södermarken  (dellokal 1), Upl</t>
+          <t>Södermarken, Häverö, Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>709537</v>
+        <v>709541</v>
       </c>
       <c r="R55" t="n">
-        <v>6663446</v>
+        <v>6663457</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7108,17 +7119,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
+          <t>2003-07-15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2004-08-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Areal: 0,6 ha (22 x 6 m). Slåttertid v.33. Veg.höjd 20 cm. Sköts fr.o.m. 2002 av Stiftelsen Norrtälje Naturvårdsfond.</t>
+          <t>2003-07-15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7132,30 +7138,30 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Slåtter</t>
+          <t>Lieslåtter 2001 - 10 ex</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Maria Pettersson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Maria Pettersson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3868565</t>
+          <t>https://artportalen.se/Sighting/3861369</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3868566</v>
+        <v>3868565</v>
       </c>
       <c r="B56" t="n">
         <v>106414</v>
@@ -7181,7 +7187,7 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7191,14 +7197,14 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Södermarken  (dellokal 2), Upl</t>
+          <t>Södermarken  (dellokal 1), Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>709521</v>
+        <v>709537</v>
       </c>
       <c r="R56" t="n">
-        <v>6663496</v>
+        <v>6663446</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7235,7 +7241,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Areal: 0,6 ha (1 x 30 m). Slåttertid v.33. Veg.höjd 20 cm</t>
+          <t>Areal: 0,6 ha (22 x 6 m). Slåttertid v.33. Veg.höjd 20 cm. Sköts fr.o.m. 2002 av Stiftelsen Norrtälje Naturvårdsfond.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7266,43 +7272,39 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3868566</t>
+          <t>https://artportalen.se/Sighting/3868565</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4532115</v>
+        <v>3868566</v>
       </c>
       <c r="B57" t="n">
-        <v>98050</v>
+        <v>106414</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222112</v>
+        <v>221447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7312,14 +7314,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken  (dellokal 2), Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>709548</v>
+        <v>709521</v>
       </c>
       <c r="R57" t="n">
-        <v>6663459</v>
+        <v>6663496</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7346,12 +7348,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-08-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-08-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Areal: 0,6 ha (1 x 30 m). Slåttertid v.33. Veg.höjd 20 cm</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7365,33 +7372,33 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
+          <t>Slåtter</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Maria Pettersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4532115</t>
+          <t>https://artportalen.se/Sighting/3868566</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4418368</v>
+        <v>4532115</v>
       </c>
       <c r="B58" t="n">
-        <v>102560</v>
+        <v>98050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7399,24 +7406,33 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222133</v>
+        <v>222112</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södermarkens slåtteräng, Upl</t>
@@ -7489,13 +7505,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4418368</t>
+          <t>https://artportalen.se/Sighting/4532115</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4427038</v>
+        <v>4418368</v>
       </c>
       <c r="B59" t="n">
         <v>102560</v>
@@ -7524,29 +7540,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng (vid Trästabron), Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>709424</v>
+        <v>709548</v>
       </c>
       <c r="R59" t="n">
-        <v>6663393</v>
+        <v>6663459</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7570,17 +7576,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2010-05-24</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2010-05-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Har precis börjat blomma.</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7594,30 +7595,30 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Friskäng, slåtteräng</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4427038</t>
+          <t>https://artportalen.se/Sighting/4418368</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111503016</v>
+        <v>4427038</v>
       </c>
       <c r="B60" t="n">
         <v>102560</v>
@@ -7646,6 +7647,11 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -7653,17 +7659,17 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Södermarken, V Trästabron, Upl</t>
+          <t>Södermarkens slåtteräng (vid Trästabron), Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>709543</v>
+        <v>709424</v>
       </c>
       <c r="R60" t="n">
-        <v>6663463</v>
+        <v>6663393</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7687,12 +7693,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2010-05-24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2010-05-24</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Har precis börjat blomma.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7706,30 +7717,30 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Naturbetesmark</t>
+          <t>Friskäng, slåtteräng</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111503016</t>
+          <t>https://artportalen.se/Sighting/4427038</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127633110</v>
+        <v>111503016</v>
       </c>
       <c r="B61" t="n">
         <v>102560</v>
@@ -7765,14 +7776,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Södermarken, V Trästabron, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>709547</v>
+        <v>709543</v>
       </c>
       <c r="R61" t="n">
-        <v>6663458</v>
+        <v>6663463</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7799,12 +7810,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7818,7 +7829,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Naturbetesmark</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7832,23 +7843,19 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127633110</t>
+          <t>https://artportalen.se/Sighting/111503016</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125294304</v>
+        <v>127633110</v>
       </c>
       <c r="B62" t="n">
-        <v>99754</v>
+        <v>102560</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7856,21 +7863,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222295</v>
+        <v>222133</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7881,14 +7888,14 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
+          <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>709463</v>
+        <v>709547</v>
       </c>
       <c r="R62" t="n">
-        <v>6663432</v>
+        <v>6663458</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7915,12 +7922,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7955,13 +7962,13 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125294304</t>
+          <t>https://artportalen.se/Sighting/127633110</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125294346</v>
+        <v>125294304</v>
       </c>
       <c r="B63" t="n">
         <v>99754</v>
@@ -8001,10 +8008,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>709383</v>
+        <v>709463</v>
       </c>
       <c r="R63" t="n">
-        <v>6663405</v>
+        <v>6663432</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8071,44 +8078,44 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125294346</t>
+          <t>https://artportalen.se/Sighting/125294304</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125294338</v>
+        <v>125294346</v>
       </c>
       <c r="B64" t="n">
-        <v>101326</v>
+        <v>99754</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>222295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8117,10 +8124,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>709424</v>
+        <v>709383</v>
       </c>
       <c r="R64" t="n">
-        <v>6663425</v>
+        <v>6663405</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8155,11 +8162,6 @@
           <t>2025-05-19</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Lite skuggigare plats.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8192,16 +8194,16 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125294338</t>
+          <t>https://artportalen.se/Sighting/125294346</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>79861531</v>
+        <v>125294338</v>
       </c>
       <c r="B65" t="n">
-        <v>99097</v>
+        <v>101326</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8209,35 +8211,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223609</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Södermarken, strax N om Trästabrons västra brofäste., Upl</t>
+          <t>Södermarken, N om Trästabrons fäste på fastlandssidan, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>709493</v>
+        <v>709424</v>
       </c>
       <c r="R65" t="n">
-        <v>6663440</v>
+        <v>6663425</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8264,12 +8270,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Lite skuggigare plats.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8278,13 +8289,12 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Äng</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8298,19 +8308,23 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79861531</t>
+          <t>https://artportalen.se/Sighting/125294338</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5994122</v>
+        <v>79861531</v>
       </c>
       <c r="B66" t="n">
-        <v>99121</v>
+        <v>99097</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8318,39 +8332,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223614</v>
+        <v>223609</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
+          <t>Epipactis helleborine subsp. helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Södermarken, strax N om Trästabrons västra brofäste., Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>709464</v>
+        <v>709493</v>
       </c>
       <c r="R66" t="n">
-        <v>6663397</v>
+        <v>6663440</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8377,17 +8387,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2009-06-26</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2009-06-26</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>3 smågrupper med 5, 2, och 5 ex</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8396,38 +8401,39 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>slåtteräng</t>
+          <t>Äng</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ebbe Zachrisson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5994122</t>
+          <t>https://artportalen.se/Sighting/79861531</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>69559092</v>
+        <v>5994122</v>
       </c>
       <c r="B67" t="n">
-        <v>99232</v>
+        <v>99121</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8435,37 +8441,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223621</v>
+        <v>223614</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Drejer) Løjtnant</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>400 m SO om Bergby, Upl</t>
+          <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>709283</v>
+        <v>709464</v>
       </c>
       <c r="R67" t="n">
-        <v>6663499</v>
+        <v>6663397</v>
       </c>
       <c r="S67" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8489,17 +8500,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2009-06-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
+          <t>2009-06-26</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>3 smågrupper med 5, 2, och 5 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8510,11 +8521,16 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>slåtteräng</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -8522,57 +8538,57 @@
           <t>Ebbe Zachrisson</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+      <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69559092</t>
+          <t>https://artportalen.se/Sighting/5994122</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2665273</v>
+        <v>69559092</v>
       </c>
       <c r="B68" t="n">
-        <v>104641</v>
+        <v>99232</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>224416</v>
+        <v>223621</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>400 m SO om Bergby, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>709548</v>
+        <v>709283</v>
       </c>
       <c r="R68" t="n">
-        <v>6663459</v>
+        <v>6663499</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8596,12 +8612,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>1998-08-05</t>
+          <t>2004-12-31</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8612,33 +8633,32 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Ohävdad slåtteräng, vid stigkorsning</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2665273</t>
+          <t>https://artportalen.se/Sighting/69559092</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>111503012</v>
+        <v>2665273</v>
       </c>
       <c r="B69" t="n">
         <v>104641</v>
@@ -8663,21 +8683,16 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Södermarken, V Trästabron, Upl</t>
+          <t>Södermarkens slåtteräng, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>709560</v>
+        <v>709548</v>
       </c>
       <c r="R69" t="n">
-        <v>6663464</v>
+        <v>6663459</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8704,12 +8719,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>1998-08-05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8723,30 +8738,30 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Naturbetesmark</t>
+          <t>Ohävdad slåtteräng, vid stigkorsning</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111503012</t>
+          <t>https://artportalen.se/Sighting/2665273</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127633113</v>
+        <v>111503012</v>
       </c>
       <c r="B70" t="n">
         <v>104641</v>
@@ -8771,24 +8786,21 @@
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Södermarken, Upl</t>
+          <t>Södermarken, V Trästabron, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>709502</v>
+        <v>709560</v>
       </c>
       <c r="R70" t="n">
-        <v>6663436</v>
+        <v>6663464</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8815,12 +8827,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8829,13 +8841,12 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Slåtteräng</t>
+          <t>Naturbetesmark</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8849,23 +8860,19 @@
           <t>Jan Yngve Andersson</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Kärlväxtinventering Södermarken</t>
-        </is>
-      </c>
+      <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127633113</t>
+          <t>https://artportalen.se/Sighting/111503012</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127633119</v>
+        <v>127633113</v>
       </c>
       <c r="B71" t="n">
-        <v>104640</v>
+        <v>104641</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8887,21 +8894,24 @@
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>709458</v>
+        <v>709502</v>
       </c>
       <c r="R71" t="n">
-        <v>6663422</v>
+        <v>6663436</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8942,6 +8952,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8968,16 +8979,16 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127633119</t>
+          <t>https://artportalen.se/Sighting/127633113</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6352562</v>
+        <v>127633119</v>
       </c>
       <c r="B72" t="n">
-        <v>101746</v>
+        <v>104640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8985,47 +8996,38 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>224932</v>
+        <v>224416</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+          <t>Helianthemum nummularium subsp. nummularium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Södermarkens slåtteräng, Upl</t>
+          <t>Södermarken, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>709519</v>
+        <v>709458</v>
       </c>
       <c r="R72" t="n">
-        <v>6663483</v>
+        <v>6663422</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9049,12 +9051,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2010-06-02</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9068,22 +9070,143 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Hävdad slåtteräng</t>
+          <t>Slåtteräng</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Kärlväxtinventering Södermarken</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127633119</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>6352562</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101746</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Södermarkens slåtteräng, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>709519</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6663483</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2010-06-02</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Hävdad slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
+      <c r="AX73" t="inlineStr">
         <is>
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6352562</t>
         </is>
@@ -9162,6 +9285,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99272</v>
+        <v>99273</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99273</v>
+        <v>99274</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99280</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99280</v>
+        <v>99281</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99281</v>
+        <v>99292</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99292</v>
+        <v>99305</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99305</v>
+        <v>99306</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99306</v>
+        <v>99319</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
